--- a/Guia_01_Bitacora/Bitacora.xlsx
+++ b/Guia_01_Bitacora/Bitacora.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fa410ce2def32c05/ESTUDIO/ADSO-Bitacora/Guia_01_Bitacora/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{944DC553-80E3-4437-A073-55773299869F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{515B7F5C-0D9A-422D-B714-E552065F567B}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{944DC553-80E3-4437-A073-55773299869F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{832B4F7D-3BF8-4A26-A86C-2B9D1E7B1968}"/>
   <bookViews>
-    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Información" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
   <si>
     <t>Versión: 01</t>
   </si>
@@ -249,12 +249,60 @@
   <si>
     <t>https://github.com/Marcosuarez02/ADSO-BITACORA/tree/main/Guia_01_Bitacora</t>
   </si>
+  <si>
+    <t>Proceder con la revisión de la bitácora del compañero.</t>
+  </si>
+  <si>
+    <t>Conformación del equipo de trabajo en parejas para el desarrollo de la actividad de auditoría.</t>
+  </si>
+  <si>
+    <t>C:\Users\marco\OneDrive\ESTUDIO\ADSO-Bitacora\Guia_01_Bitacora (enviado por correo).</t>
+  </si>
+  <si>
+    <t>06/08/2026 -13:00</t>
+  </si>
+  <si>
+    <t>30/07/2026 -18:00</t>
+  </si>
+  <si>
+    <t>30/07/2026  -14:10</t>
+  </si>
+  <si>
+    <t>30/07/2026- 15:30</t>
+  </si>
+  <si>
+    <t>30/07/2026 -13:15:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inspeccion de la bitacora del compañero usando la lista de chequeo y la matriz de auditoria. </t>
+  </si>
+  <si>
+    <t>analisis de lista de chequeo, no se lograba la identificación y  concluir con el analisis de lista de chequeo,lograr identificar y evaluar en analisis y respuesta de cada item</t>
+  </si>
+  <si>
+    <t>pasar a la fase de presentacion de auditoria y lista de chequeo de aprobacion</t>
+  </si>
+  <si>
+    <t>https://github.com/Marcosuarez02/ADSO-BITACORA/tree/main/Guia_01_Bitacora/Auditoria%20y%20lista_chequeo</t>
+  </si>
+  <si>
+    <t>06/08/2026-15:30</t>
+  </si>
+  <si>
+    <t>proceder con la realizacion de la bitacora mediante lo realizado en la formacion presente.</t>
+  </si>
+  <si>
+    <t>observacion y análisis de exposición de compañeros mediante el documento de auditoria y lista de chequeo de transferencia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://classroom.google.com/u/1/c/ODcxMDI1Mjk5NTQ4/a/ODcxMzQ0ODUyNTY5/details </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -436,7 +484,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -550,6 +598,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -994,9 +1048,9 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:AA23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="15" customHeight="1">
+    <row r="1" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -1027,7 +1081,7 @@
       </c>
       <c r="AA1" s="16"/>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -1056,7 +1110,7 @@
       <c r="Z2" s="17"/>
       <c r="AA2" s="19"/>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -1085,7 +1139,7 @@
       <c r="Z3" s="17"/>
       <c r="AA3" s="19"/>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1114,7 +1168,7 @@
       <c r="Z4" s="17"/>
       <c r="AA4" s="19"/>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="17"/>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -1143,7 +1197,7 @@
       <c r="Z5" s="17"/>
       <c r="AA5" s="19"/>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="20"/>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -1172,7 +1226,7 @@
       <c r="Z6" s="20"/>
       <c r="AA6" s="22"/>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>1</v>
       </c>
@@ -1203,7 +1257,7 @@
       <c r="Z7" s="24"/>
       <c r="AA7" s="25"/>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="26"/>
       <c r="B8" s="27"/>
       <c r="C8" s="27"/>
@@ -1232,7 +1286,7 @@
       <c r="Z8" s="27"/>
       <c r="AA8" s="28"/>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>2</v>
       </c>
@@ -1265,7 +1319,7 @@
       <c r="Z9" s="15"/>
       <c r="AA9" s="16"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="17"/>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -1294,7 +1348,7 @@
       <c r="Z10" s="18"/>
       <c r="AA10" s="19"/>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="20"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -1323,7 +1377,7 @@
       <c r="Z11" s="21"/>
       <c r="AA11" s="22"/>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>3</v>
       </c>
@@ -1356,7 +1410,7 @@
       <c r="Z12" s="15"/>
       <c r="AA12" s="16"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="17"/>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -1385,7 +1439,7 @@
       <c r="Z13" s="18"/>
       <c r="AA13" s="19"/>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="20"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -1414,7 +1468,7 @@
       <c r="Z14" s="21"/>
       <c r="AA14" s="22"/>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>4</v>
       </c>
@@ -1447,7 +1501,7 @@
       <c r="Z15" s="15"/>
       <c r="AA15" s="16"/>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="17"/>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -1476,7 +1530,7 @@
       <c r="Z16" s="18"/>
       <c r="AA16" s="19"/>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="20"/>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -1505,7 +1559,7 @@
       <c r="Z17" s="21"/>
       <c r="AA17" s="22"/>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>5</v>
       </c>
@@ -1538,7 +1592,7 @@
       <c r="Z18" s="15"/>
       <c r="AA18" s="16"/>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="17"/>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
@@ -1567,7 +1621,7 @@
       <c r="Z19" s="18"/>
       <c r="AA19" s="19"/>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="20"/>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -1596,7 +1650,7 @@
       <c r="Z20" s="21"/>
       <c r="AA20" s="22"/>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>6</v>
       </c>
@@ -1629,7 +1683,7 @@
       <c r="Z21" s="15"/>
       <c r="AA21" s="16"/>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -1658,7 +1712,7 @@
       <c r="Z22" s="18"/>
       <c r="AA22" s="19"/>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="20"/>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
@@ -1714,9 +1768,9 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AA41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -1747,7 +1801,7 @@
       </c>
       <c r="AA1" s="16"/>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -1776,7 +1830,7 @@
       <c r="Z2" s="17"/>
       <c r="AA2" s="19"/>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -1805,7 +1859,7 @@
       <c r="Z3" s="17"/>
       <c r="AA3" s="19"/>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1834,7 +1888,7 @@
       <c r="Z4" s="17"/>
       <c r="AA4" s="19"/>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="17"/>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -1863,7 +1917,7 @@
       <c r="Z5" s="17"/>
       <c r="AA5" s="19"/>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="20"/>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -1892,7 +1946,7 @@
       <c r="Z6" s="20"/>
       <c r="AA6" s="22"/>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>1</v>
       </c>
@@ -1923,7 +1977,7 @@
       <c r="Z7" s="24"/>
       <c r="AA7" s="25"/>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="26"/>
       <c r="B8" s="27"/>
       <c r="C8" s="27"/>
@@ -1952,7 +2006,7 @@
       <c r="Z8" s="27"/>
       <c r="AA8" s="28"/>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="29" t="s">
         <v>7</v>
       </c>
@@ -1983,7 +2037,7 @@
       <c r="Z9" s="29"/>
       <c r="AA9" s="29"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="30"/>
       <c r="B10" s="30"/>
       <c r="C10" s="30"/>
@@ -2012,7 +2066,7 @@
       <c r="Z10" s="30"/>
       <c r="AA10" s="30"/>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="30"/>
       <c r="B11" s="30"/>
       <c r="C11" s="30"/>
@@ -2041,7 +2095,7 @@
       <c r="Z11" s="30"/>
       <c r="AA11" s="30"/>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="30"/>
       <c r="B12" s="30"/>
       <c r="C12" s="30"/>
@@ -2070,7 +2124,7 @@
       <c r="Z12" s="30"/>
       <c r="AA12" s="30"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="30"/>
       <c r="B13" s="30"/>
       <c r="C13" s="30"/>
@@ -2099,7 +2153,7 @@
       <c r="Z13" s="30"/>
       <c r="AA13" s="30"/>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="30"/>
       <c r="B14" s="30"/>
       <c r="C14" s="30"/>
@@ -2128,7 +2182,7 @@
       <c r="Z14" s="30"/>
       <c r="AA14" s="30"/>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="30"/>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
@@ -2157,7 +2211,7 @@
       <c r="Z15" s="30"/>
       <c r="AA15" s="30"/>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="30"/>
       <c r="B16" s="30"/>
       <c r="C16" s="30"/>
@@ -2186,7 +2240,7 @@
       <c r="Z16" s="30"/>
       <c r="AA16" s="30"/>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="30"/>
       <c r="B17" s="30"/>
       <c r="C17" s="30"/>
@@ -2215,7 +2269,7 @@
       <c r="Z17" s="30"/>
       <c r="AA17" s="30"/>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="30"/>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
@@ -2244,7 +2298,7 @@
       <c r="Z18" s="30"/>
       <c r="AA18" s="30"/>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="30"/>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
@@ -2273,7 +2327,7 @@
       <c r="Z19" s="30"/>
       <c r="AA19" s="30"/>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="30"/>
       <c r="B20" s="30"/>
       <c r="C20" s="30"/>
@@ -2302,7 +2356,7 @@
       <c r="Z20" s="30"/>
       <c r="AA20" s="30"/>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="30"/>
       <c r="B21" s="30"/>
       <c r="C21" s="30"/>
@@ -2331,7 +2385,7 @@
       <c r="Z21" s="30"/>
       <c r="AA21" s="30"/>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="30"/>
       <c r="B22" s="30"/>
       <c r="C22" s="30"/>
@@ -2360,7 +2414,7 @@
       <c r="Z22" s="30"/>
       <c r="AA22" s="30"/>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="30"/>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
@@ -2389,7 +2443,7 @@
       <c r="Z23" s="30"/>
       <c r="AA23" s="30"/>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="31" t="s">
         <v>18</v>
       </c>
@@ -2420,7 +2474,7 @@
       <c r="Z24" s="32"/>
       <c r="AA24" s="32"/>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="32"/>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
@@ -2449,7 +2503,7 @@
       <c r="Z25" s="32"/>
       <c r="AA25" s="32"/>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="33" t="s">
         <v>19</v>
       </c>
@@ -2482,7 +2536,7 @@
       <c r="Z26" s="15"/>
       <c r="AA26" s="16"/>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="36"/>
       <c r="B27" s="37"/>
       <c r="C27" s="37"/>
@@ -2511,7 +2565,7 @@
       <c r="Z27" s="21"/>
       <c r="AA27" s="22"/>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" s="33" t="s">
         <v>9</v>
       </c>
@@ -2544,7 +2598,7 @@
       <c r="Z28" s="15"/>
       <c r="AA28" s="16"/>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" s="36"/>
       <c r="B29" s="37"/>
       <c r="C29" s="37"/>
@@ -2573,7 +2627,7 @@
       <c r="Z29" s="21"/>
       <c r="AA29" s="22"/>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" s="33" t="s">
         <v>10</v>
       </c>
@@ -2606,7 +2660,7 @@
       <c r="Z30" s="15"/>
       <c r="AA30" s="16"/>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="36"/>
       <c r="B31" s="37"/>
       <c r="C31" s="37"/>
@@ -2635,7 +2689,7 @@
       <c r="Z31" s="21"/>
       <c r="AA31" s="22"/>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" s="33" t="s">
         <v>11</v>
       </c>
@@ -2668,7 +2722,7 @@
       <c r="Z32" s="15"/>
       <c r="AA32" s="16"/>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" s="36"/>
       <c r="B33" s="37"/>
       <c r="C33" s="37"/>
@@ -2697,7 +2751,7 @@
       <c r="Z33" s="21"/>
       <c r="AA33" s="22"/>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" s="33" t="s">
         <v>12</v>
       </c>
@@ -2730,7 +2784,7 @@
       <c r="Z34" s="15"/>
       <c r="AA34" s="16"/>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35" s="36"/>
       <c r="B35" s="37"/>
       <c r="C35" s="37"/>
@@ -2759,7 +2813,7 @@
       <c r="Z35" s="21"/>
       <c r="AA35" s="22"/>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="33" t="s">
         <v>13</v>
       </c>
@@ -2792,7 +2846,7 @@
       <c r="Z36" s="15"/>
       <c r="AA36" s="16"/>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" s="36"/>
       <c r="B37" s="37"/>
       <c r="C37" s="37"/>
@@ -2821,7 +2875,7 @@
       <c r="Z37" s="21"/>
       <c r="AA37" s="22"/>
     </row>
-    <row r="38" spans="1:27">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" s="33" t="s">
         <v>26</v>
       </c>
@@ -2854,7 +2908,7 @@
       <c r="Z38" s="15"/>
       <c r="AA38" s="16"/>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" s="36"/>
       <c r="B39" s="37"/>
       <c r="C39" s="37"/>
@@ -2883,7 +2937,7 @@
       <c r="Z39" s="21"/>
       <c r="AA39" s="22"/>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" s="33" t="s">
         <v>28</v>
       </c>
@@ -2916,7 +2970,7 @@
       <c r="Z40" s="15"/>
       <c r="AA40" s="16"/>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" s="36"/>
       <c r="B41" s="37"/>
       <c r="C41" s="37"/>
@@ -2980,9 +3034,12 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:AA61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3013,7 +3070,7 @@
       </c>
       <c r="AA1" s="16"/>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -3042,7 +3099,7 @@
       <c r="Z2" s="17"/>
       <c r="AA2" s="19"/>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -3071,7 +3128,7 @@
       <c r="Z3" s="17"/>
       <c r="AA3" s="19"/>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -3100,7 +3157,7 @@
       <c r="Z4" s="17"/>
       <c r="AA4" s="19"/>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="17"/>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -3129,7 +3186,7 @@
       <c r="Z5" s="17"/>
       <c r="AA5" s="19"/>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="20"/>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -3158,7 +3215,7 @@
       <c r="Z6" s="20"/>
       <c r="AA6" s="22"/>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>1</v>
       </c>
@@ -3189,7 +3246,7 @@
       <c r="Z7" s="24"/>
       <c r="AA7" s="25"/>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="26"/>
       <c r="B8" s="27"/>
       <c r="C8" s="27"/>
@@ -3218,7 +3275,7 @@
       <c r="Z8" s="27"/>
       <c r="AA8" s="28"/>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>8</v>
       </c>
@@ -3249,7 +3306,7 @@
       <c r="Z9" s="15"/>
       <c r="AA9" s="16"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="17"/>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -3278,7 +3335,7 @@
       <c r="Z10" s="18"/>
       <c r="AA10" s="19"/>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="20"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -3307,7 +3364,7 @@
       <c r="Z11" s="21"/>
       <c r="AA11" s="22"/>
     </row>
-    <row r="12" spans="1:27" ht="15" customHeight="1">
+    <row r="12" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>9</v>
       </c>
@@ -3350,7 +3407,7 @@
       <c r="Z12" s="12"/>
       <c r="AA12" s="10"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="11"/>
@@ -3379,12 +3436,12 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="11"/>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>1</v>
       </c>
-      <c r="B14" s="4">
-        <v>46233.552083333336</v>
+      <c r="B14" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
@@ -3422,7 +3479,7 @@
       <c r="Z14" s="6"/>
       <c r="AA14" s="6"/>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -3451,7 +3508,7 @@
       <c r="Z15" s="6"/>
       <c r="AA15" s="6"/>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -3480,7 +3537,7 @@
       <c r="Z16" s="6"/>
       <c r="AA16" s="6"/>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -3509,12 +3566,12 @@
       <c r="Z17" s="6"/>
       <c r="AA17" s="6"/>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>2</v>
       </c>
-      <c r="B18" s="4">
-        <v>46233.590277777781</v>
+      <c r="B18" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
@@ -3552,7 +3609,7 @@
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -3581,7 +3638,7 @@
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -3610,7 +3667,7 @@
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -3639,12 +3696,12 @@
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>3</v>
       </c>
-      <c r="B22" s="4">
-        <v>46233.645833333336</v>
+      <c r="B22" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
@@ -3682,7 +3739,7 @@
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -3711,7 +3768,7 @@
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -3740,7 +3797,7 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3769,12 +3826,12 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>4</v>
       </c>
-      <c r="B26" s="4">
-        <v>46233.75</v>
+      <c r="B26" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
@@ -3812,7 +3869,7 @@
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3841,7 +3898,7 @@
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3870,7 +3927,7 @@
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3899,39 +3956,53 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="3"/>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>5</v>
+      </c>
+      <c r="B30" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="40"/>
+      <c r="D30" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
+      <c r="L30" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
+      <c r="Q30" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
+      <c r="V30" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -3957,10 +4028,10 @@
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -3986,10 +4057,10 @@
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -4015,36 +4086,50 @@
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
     </row>
-    <row r="34" spans="1:27">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>6</v>
+      </c>
+      <c r="B34" s="4">
+        <v>46240.583333333336</v>
+      </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="3"/>
+      <c r="D34" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="1"/>
+      <c r="G34" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
+      <c r="L34" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
+      <c r="V34" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -4073,7 +4158,7 @@
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -4102,7 +4187,7 @@
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4131,36 +4216,50 @@
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
     </row>
-    <row r="38" spans="1:27">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>7</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="3"/>
+      <c r="D38" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
-      <c r="G38" s="1"/>
+      <c r="G38" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="L38" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
+      <c r="Q38" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
+      <c r="V38" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4189,7 +4288,7 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4218,7 +4317,7 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -4247,7 +4346,7 @@
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4276,7 +4375,7 @@
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
     </row>
-    <row r="43" spans="1:27">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4305,7 +4404,7 @@
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
     </row>
-    <row r="44" spans="1:27">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4334,7 +4433,7 @@
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
     </row>
-    <row r="45" spans="1:27">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4363,7 +4462,7 @@
       <c r="Z45" s="1"/>
       <c r="AA45" s="1"/>
     </row>
-    <row r="46" spans="1:27">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4392,7 +4491,7 @@
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
     </row>
-    <row r="47" spans="1:27">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4421,7 +4520,7 @@
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4450,7 +4549,7 @@
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
     </row>
-    <row r="49" spans="1:27">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -4479,7 +4578,7 @@
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
     </row>
-    <row r="50" spans="1:27">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -4508,7 +4607,7 @@
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
     </row>
-    <row r="51" spans="1:27">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -4537,7 +4636,7 @@
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
     </row>
-    <row r="52" spans="1:27">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -4566,7 +4665,7 @@
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
     </row>
-    <row r="53" spans="1:27">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -4595,7 +4694,7 @@
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
     </row>
-    <row r="54" spans="1:27">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -4624,7 +4723,7 @@
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
     </row>
-    <row r="55" spans="1:27">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -4653,7 +4752,7 @@
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
     </row>
-    <row r="56" spans="1:27">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -4682,7 +4781,7 @@
       <c r="Z56" s="1"/>
       <c r="AA56" s="1"/>
     </row>
-    <row r="57" spans="1:27">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -4711,7 +4810,7 @@
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
     </row>
-    <row r="58" spans="1:27">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -4740,7 +4839,7 @@
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
     </row>
-    <row r="59" spans="1:27">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -4769,7 +4868,7 @@
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
     </row>
-    <row r="60" spans="1:27">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -4798,7 +4897,7 @@
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
     </row>
-    <row r="61" spans="1:27">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -4930,8 +5029,11 @@
     <hyperlink ref="L22" r:id="rId2" xr:uid="{9C8A05E0-C81D-4016-B25E-1CC38F0F00F6}"/>
     <hyperlink ref="L14" r:id="rId3" xr:uid="{277E2804-4026-48FB-B704-D3F2CB033B56}"/>
     <hyperlink ref="L26" r:id="rId4" xr:uid="{DF6CEB84-A9B9-46CE-9213-9580928CB449}"/>
+    <hyperlink ref="L34" r:id="rId5" xr:uid="{47CABE45-A0EC-4D11-8BD7-5EE5BC208CBA}"/>
+    <hyperlink ref="L38" r:id="rId6" xr:uid="{82E3071D-5E16-48DE-A688-16F43CC2C1C1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <drawing r:id="rId8"/>
 </worksheet>
 </file>